--- a/Result/profitability/2464.xlsx
+++ b/Result/profitability/2464.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.87</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.125</v>
       </c>
       <c r="N2" t="n">
-        <v>19.60625</v>
+        <v>19.84125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2025</v>
+        <v>0.2175</v>
       </c>
       <c r="N3" t="n">
-        <v>19.99125</v>
+        <v>20.70875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.71</v>
       </c>
       <c r="M4" t="n">
-        <v>0.25375</v>
+        <v>0.30375</v>
       </c>
       <c r="N4" t="n">
-        <v>20.7075</v>
+        <v>21.26875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>0.29375</v>
+        <v>0.42125</v>
       </c>
       <c r="N5" t="n">
-        <v>20.70375</v>
+        <v>20.8775</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.44</v>
       </c>
       <c r="M6" t="n">
-        <v>0.42375</v>
+        <v>0.475</v>
       </c>
       <c r="N6" t="n">
-        <v>20.805</v>
+        <v>21.26125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>0.465</v>
+        <v>0.55</v>
       </c>
       <c r="N7" t="n">
-        <v>21.42625</v>
+        <v>21.995</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.67</v>
       </c>
       <c r="M8" t="n">
-        <v>0.58125</v>
+        <v>0.60375</v>
       </c>
       <c r="N8" t="n">
-        <v>22.9175</v>
+        <v>23.355</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.6</v>
       </c>
       <c r="M9" t="n">
-        <v>0.62625</v>
+        <v>0.6262500000000001</v>
       </c>
       <c r="N9" t="n">
         <v>23.71125</v>
@@ -1645,7 +1645,7 @@
         <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>0.58</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>22.62625</v>
@@ -1772,7 +1772,7 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5762499999999999</v>
+        <v>0.57625</v>
       </c>
       <c r="N11" t="n">
         <v>22.82</v>
@@ -1899,7 +1899,7 @@
         <v>1.03</v>
       </c>
       <c r="M12" t="n">
-        <v>0.61625</v>
+        <v>0.6162500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>22.9825</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2464</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2169</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1688</v>
+      </c>
+      <c r="E75" t="n">
+        <v>481</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>134</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.19%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-33</v>
+      </c>
+      <c r="J75" t="n">
+        <v>101</v>
+      </c>
+      <c r="K75" t="n">
+        <v>86</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.02875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1874665238350295</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.390000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.06689124157844084</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
